--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\Oz_StudyTogether_6\MainProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\2D_Evaulation\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -21,91 +21,91 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Sword_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Coin_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Sword_1</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0_Nara_Resource/Icon/Icon_Item_Sword_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0_Nara_Resource/Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0_Nara_Resource/Icon/Icon_Item_Coin_1</x:t>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Coin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Sword_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -240,13 +240,13 @@
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -255,28 +255,28 @@
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -898,80 +898,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -980,7 +980,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -990,19 +990,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1011,7 +1011,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1021,19 +1021,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>1</x:v>
@@ -1042,7 +1042,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -2250,7 +2250,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -19,7 +19,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Coin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
   <x:si>
     <x:t>화폐</x:t>
   </x:si>
@@ -27,85 +87,34 @@
     <x:t>검</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>물약</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Sword_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Potion_1</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Sword_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Coin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
+    <x:t>Icon/Icon_Item_Sword_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Coin_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Coin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Sword_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -898,80 +907,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -980,7 +989,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -990,19 +999,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1011,7 +1020,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1021,19 +1030,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>1</x:v>
@@ -1042,7 +1051,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1050,14 +1059,26 @@
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
+      <x:c r="A7" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="4"/>
-      <x:c r="E7" s="4"/>
-      <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
-      <x:c r="H7" s="4"/>
+      <x:c r="E7" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F7" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -19,15 +19,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+  <x:si>
+    <x:t>Icon/Icon_Item_Potato</x:t>
+  </x:si>
   <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Coin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Corn</x:t>
@@ -36,58 +72,28 @@
     <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
     <x:t>Normal</x:t>
   </x:si>
   <x:si>
     <x:t>Grade</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Coin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물약</x:t>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
   </x:si>
   <x:si>
     <x:t>MaxStackCount</x:t>
@@ -96,9 +102,6 @@
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
@@ -108,13 +111,19 @@
     <x:t>Item_Potion_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Sword_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Coin_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -907,80 +916,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -989,7 +998,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -999,19 +1008,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1020,7 +1029,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1030,19 +1039,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>1</x:v>
@@ -1051,7 +1060,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1060,15 +1069,15 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1077,7 +1086,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1086,14 +1095,26 @@
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
+      <x:c r="A8" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C8" s="3"/>
       <x:c r="D8" s="4"/>
-      <x:c r="E8" s="4"/>
-      <x:c r="F8" s="4"/>
-      <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
+      <x:c r="E8" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F8" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -21,109 +21,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <x:si>
+    <x:t>Icon/Icon_Item_Coin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Potato</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Sword_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Coin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
     <x:t>지역에 나타나는 금화</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Coin_1</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>물약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물약</x:t>
-  </x:si>
-  <x:si>
     <x:t>검</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Sword_1</x:t>
   </x:si>
   <x:si>
     <x:t>착용하면 공격력이 강해진다.</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Sword_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Sword_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Coin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -916,80 +916,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -998,7 +998,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1008,19 +1008,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1029,7 +1029,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1039,19 +1039,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>1</x:v>
@@ -1060,7 +1060,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1069,15 +1069,15 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1086,7 +1086,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1096,15 +1096,15 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>100</x:v>
@@ -1113,7 +1113,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
